--- a/config/默认配置/2.报表采集系统_配置.xlsx
+++ b/config/默认配置/2.报表采集系统_配置.xlsx
@@ -142,6 +142,85 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/s2InstitutionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
+<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:authors>
+    <x:author>User</x:author>
+  </x:authors>
+  <x:commentList>
+    <x:comment ref="A1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：备用机构匹配字段，同时作为审核结果中的机构名称。
+匹配顺序：先按社会信用代码匹配，未命中时再按源数据中的机构名称匹配。源名称优先读取指标20201001，部分文件格式可回退文件名。
+调整范围：代码能稳定匹配时，可调整配置名称作为输出名称；依赖名称匹配时，须与源名称一致。建议保留正式名称。
+表头保持“机构名称”，可调整列顺序。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="B1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：机构身份主匹配键，同时输出到审核结果。
+源数据对应：优先读取机构代码指标20201002；缺失时根据文件格式回退文件名中的机构代码或banks格式的工作表名。先按代码匹配机构参照，未命中才按机构名称匹配。
+外部对应：用于查找外部文件“参照表”中的“统一社会信用代码”，再获取对应“报表项目”。
+调整范围：保持准确、稳定，建议以文本保存并保留前导零。通常不应作为展示文字随意修改。
+表头保持“社会信用代码”，兼容“机构代码”，两者不要同时设置。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="C1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：将配置的机构类别补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+调整范围：可按管理分类需要填写或调整，也可留空；修改后结果中的机构类别随之变化。
+表头保持“机构类别”，可调整列顺序。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：将配置的承接行补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+调整范围：可按管理归属需要填写或调整，也可留空；修改后结果中的承接行随之变化。
+表头保持“承接行”，可调整列顺序。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：将配置的地区补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+调整范围：可按管理地区需要填写或调整，也可留空；修改后结果中的地区随之变化。
+表头建议保持“地区”，兼容“归属行”；两者不要同时设置。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：外部核对的备用机构行标签，不直接输出到审核结果。
+对应对象：外部文件“集中系统数据”中的机构行标签，应准确对应（按去除首尾空格后的文本匹配，不做模糊匹配）。
+优先级：先用机构代码查外部文件“参照表”的“统一社会信用代码→报表项目”映射；没有该代码映射时，才回退使用本列。只修改本列不一定改变实际取数对象。
+调整范围：跟随外部机构行标签维护；需要回退匹配时不可随意改成展示名称。
+表头保持“报表项目”，可调整列顺序。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>用途：控制是否加载本行机构参照映射，不直接输出。
+填“是”会跳过此行映射；填“否”或留空会加载。兼容1/true/y/yes表示禁用。
+注意：禁用映射不等于排除该机构或停止审核。源文件仍可能被导入，并按源机构代码/名称继续处理；配置中的地区、承接行、机构类别等补充信息可能不再带入。
+表头保持“禁用”，可调整列顺序。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+  </x:commentList>
+</x:comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -555,6 +634,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdS2HeaderVml"/>
 </worksheet>
 </file>
 

--- a/config/默认配置/2.报表采集系统_配置.xlsx
+++ b/config/默认配置/2.报表采集系统_配置.xlsx
@@ -15,7 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外部核对规则" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通用设置" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'校验规则'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'环比策略'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'外部核对规则'!$A$1:$G$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -142,83 +146,69 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/s2InstitutionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author>User</x:author>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：备用机构匹配字段，同时作为审核结果中的机构名称。
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：备用机构匹配字段，同时作为审核结果中的机构名称。
 匹配顺序：先按社会信用代码匹配，未命中时再按源数据中的机构名称匹配。源名称优先读取指标20201001，部分文件格式可回退文件名。
 调整范围：代码能稳定匹配时，可调整配置名称作为输出名称；依赖名称匹配时，须与源名称一致。建议保留正式名称。
-表头保持“机构名称”，可调整列顺序。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="B1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：机构身份主匹配键，同时输出到审核结果。
+表头保持“机构名称”，可调整列顺序。</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：机构身份主匹配键，同时输出到审核结果。
 源数据对应：优先读取机构代码指标20201002；缺失时根据文件格式回退文件名中的机构代码或banks格式的工作表名。先按代码匹配机构参照，未命中才按机构名称匹配。
 外部对应：用于查找外部文件“参照表”中的“统一社会信用代码”，再获取对应“报表项目”。
 调整范围：保持准确、稳定，建议以文本保存并保留前导零。通常不应作为展示文字随意修改。
-表头保持“社会信用代码”，兼容“机构代码”，两者不要同时设置。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="C1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：将配置的机构类别补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+表头保持“社会信用代码”，兼容“机构代码”，两者不要同时设置。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：将配置的机构类别补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
 调整范围：可按管理分类需要填写或调整，也可留空；修改后结果中的机构类别随之变化。
-表头保持“机构类别”，可调整列顺序。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="D1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：将配置的承接行补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+表头保持“机构类别”，可调整列顺序。</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：将配置的承接行补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
 调整范围：可按管理归属需要填写或调整，也可留空；修改后结果中的承接行随之变化。
-表头保持“承接行”，可调整列顺序。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="E1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：将配置的地区补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
+表头保持“承接行”，可调整列顺序。</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：将配置的地区补充到审核结果中，不用于当前S2源文件或外部文件的机构匹配。
 调整范围：可按管理地区需要填写或调整，也可留空；修改后结果中的地区随之变化。
-表头建议保持“地区”，兼容“归属行”；两者不要同时设置。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="F1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：外部核对的备用机构行标签，不直接输出到审核结果。
+表头建议保持“地区”，兼容“归属行”；两者不要同时设置。</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：外部核对的备用机构行标签，不直接输出到审核结果。
 对应对象：外部文件“集中系统数据”中的机构行标签，应准确对应（按去除首尾空格后的文本匹配，不做模糊匹配）。
 优先级：先用机构代码查外部文件“参照表”的“统一社会信用代码→报表项目”映射；没有该代码映射时，才回退使用本列。只修改本列不一定改变实际取数对象。
 调整范围：跟随外部机构行标签维护；需要回退匹配时不可随意改成展示名称。
-表头保持“报表项目”，可调整列顺序。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="G1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>用途：控制是否加载本行机构参照映射，不直接输出。
+表头保持“报表项目”，可调整列顺序。</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>用途：控制是否加载本行机构参照映射，不直接输出。
 填“是”会跳过此行映射；填“否”或留空会加载。兼容1/true/y/yes表示禁用。
 注意：禁用映射不等于排除该机构或停止审核。源文件仍可能被导入，并按源机构代码/名称继续处理；配置中的地区、承接行、机构类别等补充信息可能不再带入。
-表头保持“禁用”，可调整列顺序。</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
+表头保持“禁用”，可调整列顺序。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -634,7 +624,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdS2HeaderVml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -685,6 +675,12 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="审核级别无效" error="审核级别只能选择硬性或软性。" promptTitle="选择审核级别" prompt="硬性对应旧严重/错误；软性合并旧提示/关注/核实。该级别用于筛选，不改变流程是否阻断。" type="list">
+      <formula1>"硬性,软性"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -741,6 +737,12 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="审核级别无效" error="审核级别只能选择硬性或软性。" promptTitle="选择审核级别" prompt="硬性对应旧严重/错误；软性合并旧提示/关注/核实。该级别用于筛选，不改变流程是否阻断。" type="list">
+      <formula1>"硬性,软性"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -792,6 +794,12 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="审核级别无效" error="审核级别只能选择硬性或软性。" promptTitle="选择审核级别" prompt="硬性对应旧严重/错误；软性合并旧提示/关注/核实。该级别用于筛选，不改变流程是否阻断。" type="list">
+      <formula1>"硬性,软性"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
